--- a/BaoCaoMau.xlsx
+++ b/BaoCaoMau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AI\AI_giao_duc\Au-Viet-My\ChamCong_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76853C4-BF69-47DD-9311-FE5EE60BC4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B795F679-03C4-4622-A71A-CA0CBA295295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
   <si>
     <t>THỨ 2</t>
   </si>
@@ -169,12 +169,6 @@
   </si>
   <si>
     <t>Xác nhận</t>
-  </si>
-  <si>
-    <t>Văn-C.Tiền</t>
-  </si>
-  <si>
-    <t>NGUYỄN VĂN GIANG</t>
   </si>
 </sst>
 </file>
@@ -1099,6 +1093,126 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1139,126 +1253,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1705,11 +1699,11 @@
       <c r="U1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="8"/>
@@ -1722,41 +1716,39 @@
         <v>23</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
       <c r="T2" s="10"/>
-      <c r="U2" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="U2" s="11"/>
     </row>
     <row r="3" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="91"/>
-      <c r="T3" s="91"/>
-      <c r="U3" s="92"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="131"/>
+      <c r="U3" s="132"/>
     </row>
     <row r="4" spans="1:25" ht="15.4" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
@@ -1779,49 +1771,49 @@
         <v>8</v>
       </c>
       <c r="R4" s="16"/>
-      <c r="S4" s="99">
+      <c r="S4" s="139">
         <v>3</v>
       </c>
-      <c r="T4" s="99"/>
+      <c r="T4" s="139"/>
       <c r="U4" s="17"/>
       <c r="W4" s="18"/>
     </row>
     <row r="5" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95" t="s">
+      <c r="B5" s="134"/>
+      <c r="C5" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95" t="s">
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95" t="s">
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95" t="s">
+      <c r="J5" s="135"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95" t="s">
+      <c r="M5" s="135"/>
+      <c r="N5" s="135"/>
+      <c r="O5" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="96" t="s">
+      <c r="P5" s="135"/>
+      <c r="Q5" s="135"/>
+      <c r="R5" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="98"/>
+      <c r="S5" s="137"/>
+      <c r="T5" s="137"/>
+      <c r="U5" s="138"/>
       <c r="W5" s="19"/>
     </row>
     <row r="6" spans="1:25" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1885,7 +1877,7 @@
       <c r="W6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="109" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="31">
@@ -1964,7 +1956,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="125"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="31">
         <v>2</v>
       </c>
@@ -2039,7 +2031,7 @@
       <c r="U8" s="42"/>
     </row>
     <row r="9" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="125"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="31">
         <v>3</v>
       </c>
@@ -2116,7 +2108,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
+      <c r="A10" s="109"/>
       <c r="B10" s="31">
         <v>4</v>
       </c>
@@ -2188,13 +2180,13 @@
         <v/>
       </c>
       <c r="T10" s="41"/>
-      <c r="U10" s="116">
+      <c r="U10" s="104">
         <f ca="1">SUM(S7:S13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="125"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="44"/>
       <c r="C11" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -2264,10 +2256,10 @@
         <v/>
       </c>
       <c r="T11" s="41"/>
-      <c r="U11" s="116"/>
+      <c r="U11" s="104"/>
     </row>
     <row r="12" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="125"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="31">
         <v>5</v>
       </c>
@@ -2339,10 +2331,10 @@
         <v/>
       </c>
       <c r="T12" s="41"/>
-      <c r="U12" s="116"/>
+      <c r="U12" s="104"/>
     </row>
     <row r="13" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="125"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="31">
         <v>6</v>
       </c>
@@ -2414,10 +2406,10 @@
         <v/>
       </c>
       <c r="T13" s="41"/>
-      <c r="U13" s="116"/>
+      <c r="U13" s="104"/>
     </row>
     <row r="14" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="125"/>
+      <c r="A14" s="109"/>
       <c r="B14" s="31">
         <v>7</v>
       </c>
@@ -2481,10 +2473,10 @@
       <c r="R14" s="45"/>
       <c r="S14" s="46"/>
       <c r="T14" s="41"/>
-      <c r="U14" s="116"/>
+      <c r="U14" s="104"/>
     </row>
     <row r="15" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="125"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="31">
         <v>8</v>
       </c>
@@ -2548,7 +2540,7 @@
       <c r="R15" s="45"/>
       <c r="S15" s="46"/>
       <c r="T15" s="41"/>
-      <c r="U15" s="116"/>
+      <c r="U15" s="104"/>
     </row>
     <row r="16" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="47"/>
@@ -2613,13 +2605,13 @@
       <c r="R16" s="49"/>
       <c r="S16" s="50"/>
       <c r="T16" s="51"/>
-      <c r="U16" s="117"/>
+      <c r="U16" s="105"/>
       <c r="V16"/>
       <c r="X16"/>
       <c r="Y16"/>
     </row>
     <row r="17" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="108" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="53">
@@ -2690,12 +2682,12 @@
         <v/>
       </c>
       <c r="T17" s="37"/>
-      <c r="U17" s="112" t="s">
+      <c r="U17" s="106" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="124"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="53">
         <v>2</v>
       </c>
@@ -2758,10 +2750,10 @@
         <v/>
       </c>
       <c r="T18" s="41"/>
-      <c r="U18" s="113"/>
+      <c r="U18" s="107"/>
     </row>
     <row r="19" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="124"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="53">
         <v>3</v>
       </c>
@@ -2829,7 +2821,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="124"/>
+      <c r="A20" s="108"/>
       <c r="B20" s="53">
         <v>4</v>
       </c>
@@ -2892,13 +2884,13 @@
         <v/>
       </c>
       <c r="T20" s="41"/>
-      <c r="U20" s="116">
+      <c r="U20" s="104">
         <f ca="1">SUM(S17:S23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="124"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="55"/>
       <c r="C21" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -2959,10 +2951,10 @@
         <v/>
       </c>
       <c r="T21" s="41"/>
-      <c r="U21" s="116"/>
+      <c r="U21" s="104"/>
     </row>
     <row r="22" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="124"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="53">
         <v>5</v>
       </c>
@@ -3025,10 +3017,10 @@
         <v/>
       </c>
       <c r="T22" s="41"/>
-      <c r="U22" s="116"/>
+      <c r="U22" s="104"/>
     </row>
     <row r="23" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="53">
         <v>6</v>
       </c>
@@ -3091,10 +3083,10 @@
         <v/>
       </c>
       <c r="T23" s="41"/>
-      <c r="U23" s="116"/>
+      <c r="U23" s="104"/>
     </row>
     <row r="24" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="124"/>
+      <c r="A24" s="108"/>
       <c r="B24" s="53">
         <v>7</v>
       </c>
@@ -3152,10 +3144,10 @@
       <c r="R24" s="45"/>
       <c r="S24" s="46"/>
       <c r="T24" s="41"/>
-      <c r="U24" s="116"/>
+      <c r="U24" s="104"/>
     </row>
     <row r="25" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="124"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="53">
         <v>8</v>
       </c>
@@ -3213,7 +3205,7 @@
       <c r="R25" s="45"/>
       <c r="S25" s="46"/>
       <c r="T25" s="41"/>
-      <c r="U25" s="116"/>
+      <c r="U25" s="104"/>
     </row>
     <row r="26" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="47"/>
@@ -3272,12 +3264,12 @@
       <c r="R26" s="49"/>
       <c r="S26" s="50"/>
       <c r="T26" s="51"/>
-      <c r="U26" s="117"/>
+      <c r="U26" s="105"/>
       <c r="X26"/>
       <c r="Y26"/>
     </row>
     <row r="27" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="109" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="31">
@@ -3342,12 +3334,12 @@
         <v/>
       </c>
       <c r="T27" s="37"/>
-      <c r="U27" s="112" t="s">
+      <c r="U27" s="106" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="125"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="31">
         <v>2</v>
       </c>
@@ -3410,10 +3402,10 @@
         <v/>
       </c>
       <c r="T28" s="41"/>
-      <c r="U28" s="113"/>
+      <c r="U28" s="107"/>
     </row>
     <row r="29" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="125"/>
+      <c r="A29" s="109"/>
       <c r="B29" s="31">
         <v>3</v>
       </c>
@@ -3481,7 +3473,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="125"/>
+      <c r="A30" s="109"/>
       <c r="B30" s="31">
         <v>4</v>
       </c>
@@ -3544,13 +3536,13 @@
         <v/>
       </c>
       <c r="T30" s="41"/>
-      <c r="U30" s="116">
+      <c r="U30" s="104">
         <f ca="1">SUM(S27:S33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="125"/>
+      <c r="A31" s="109"/>
       <c r="B31" s="44"/>
       <c r="C31" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -3611,10 +3603,10 @@
         <v/>
       </c>
       <c r="T31" s="41"/>
-      <c r="U31" s="116"/>
+      <c r="U31" s="104"/>
     </row>
     <row r="32" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="125"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="31">
         <v>5</v>
       </c>
@@ -3677,10 +3669,10 @@
         <v/>
       </c>
       <c r="T32" s="41"/>
-      <c r="U32" s="116"/>
+      <c r="U32" s="104"/>
     </row>
     <row r="33" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="125"/>
+      <c r="A33" s="109"/>
       <c r="B33" s="31">
         <v>6</v>
       </c>
@@ -3743,10 +3735,10 @@
         <v/>
       </c>
       <c r="T33" s="41"/>
-      <c r="U33" s="116"/>
+      <c r="U33" s="104"/>
     </row>
     <row r="34" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="125"/>
+      <c r="A34" s="109"/>
       <c r="B34" s="31">
         <v>7</v>
       </c>
@@ -3804,10 +3796,10 @@
       <c r="R34" s="45"/>
       <c r="S34" s="46"/>
       <c r="T34" s="41"/>
-      <c r="U34" s="116"/>
+      <c r="U34" s="104"/>
     </row>
     <row r="35" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="125"/>
+      <c r="A35" s="109"/>
       <c r="B35" s="31">
         <v>8</v>
       </c>
@@ -3865,7 +3857,7 @@
       <c r="R35" s="45"/>
       <c r="S35" s="46"/>
       <c r="T35" s="41"/>
-      <c r="U35" s="116"/>
+      <c r="U35" s="104"/>
     </row>
     <row r="36" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="47"/>
@@ -3924,12 +3916,12 @@
       <c r="R36" s="49"/>
       <c r="S36" s="50"/>
       <c r="T36" s="51"/>
-      <c r="U36" s="117"/>
+      <c r="U36" s="105"/>
       <c r="X36"/>
       <c r="Y36"/>
     </row>
     <row r="37" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="124" t="s">
+      <c r="A37" s="108" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="53">
@@ -3994,12 +3986,12 @@
         <v/>
       </c>
       <c r="T37" s="37"/>
-      <c r="U37" s="112" t="s">
+      <c r="U37" s="106" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="124"/>
+      <c r="A38" s="108"/>
       <c r="B38" s="53">
         <v>2</v>
       </c>
@@ -4062,10 +4054,10 @@
         <v/>
       </c>
       <c r="T38" s="41"/>
-      <c r="U38" s="113"/>
+      <c r="U38" s="107"/>
     </row>
     <row r="39" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="124"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="53">
         <v>3</v>
       </c>
@@ -4142,7 +4134,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="124"/>
+      <c r="A40" s="108"/>
       <c r="B40" s="53">
         <v>4</v>
       </c>
@@ -4211,13 +4203,13 @@
         <v/>
       </c>
       <c r="T40" s="41"/>
-      <c r="U40" s="116">
+      <c r="U40" s="104">
         <f ca="1">SUM(S37:S43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="124"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="56"/>
       <c r="C41" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -4287,10 +4279,10 @@
         <v/>
       </c>
       <c r="T41" s="41"/>
-      <c r="U41" s="116"/>
+      <c r="U41" s="104"/>
     </row>
     <row r="42" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="124"/>
+      <c r="A42" s="108"/>
       <c r="B42" s="53">
         <v>5</v>
       </c>
@@ -4362,10 +4354,10 @@
         <v/>
       </c>
       <c r="T42" s="41"/>
-      <c r="U42" s="116"/>
+      <c r="U42" s="104"/>
     </row>
     <row r="43" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="124"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="53">
         <v>6</v>
       </c>
@@ -4437,10 +4429,10 @@
         <v/>
       </c>
       <c r="T43" s="41"/>
-      <c r="U43" s="116"/>
+      <c r="U43" s="104"/>
     </row>
     <row r="44" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="124"/>
+      <c r="A44" s="108"/>
       <c r="B44" s="53">
         <v>7</v>
       </c>
@@ -4507,10 +4499,10 @@
       <c r="R44" s="45"/>
       <c r="S44" s="46"/>
       <c r="T44" s="41"/>
-      <c r="U44" s="116"/>
+      <c r="U44" s="104"/>
     </row>
     <row r="45" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="124"/>
+      <c r="A45" s="108"/>
       <c r="B45" s="53">
         <v>8</v>
       </c>
@@ -4577,7 +4569,7 @@
       <c r="R45" s="45"/>
       <c r="S45" s="46"/>
       <c r="T45" s="41"/>
-      <c r="U45" s="116"/>
+      <c r="U45" s="104"/>
     </row>
     <row r="46" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="57"/>
@@ -4645,12 +4637,12 @@
       <c r="R46" s="49"/>
       <c r="S46" s="50"/>
       <c r="T46" s="51"/>
-      <c r="U46" s="117"/>
+      <c r="U46" s="105"/>
       <c r="X46"/>
       <c r="Y46"/>
     </row>
     <row r="47" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="109" t="s">
+      <c r="A47" s="117" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="31">
@@ -4724,12 +4716,12 @@
         <v/>
       </c>
       <c r="T47" s="37"/>
-      <c r="U47" s="112" t="s">
+      <c r="U47" s="106" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="110"/>
+      <c r="A48" s="118"/>
       <c r="B48" s="31">
         <v>2</v>
       </c>
@@ -4801,10 +4793,10 @@
         <v/>
       </c>
       <c r="T48" s="41"/>
-      <c r="U48" s="113"/>
+      <c r="U48" s="107"/>
     </row>
     <row r="49" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="110"/>
+      <c r="A49" s="118"/>
       <c r="B49" s="31">
         <v>3</v>
       </c>
@@ -4881,7 +4873,7 @@
       </c>
     </row>
     <row r="50" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="110"/>
+      <c r="A50" s="118"/>
       <c r="B50" s="31">
         <v>4</v>
       </c>
@@ -4953,12 +4945,12 @@
         <v/>
       </c>
       <c r="T50" s="41"/>
-      <c r="U50" s="116">
+      <c r="U50" s="104">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="110"/>
+      <c r="A51" s="118"/>
       <c r="B51" s="44"/>
       <c r="C51" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -5028,10 +5020,10 @@
         <v/>
       </c>
       <c r="T51" s="41"/>
-      <c r="U51" s="116"/>
+      <c r="U51" s="104"/>
     </row>
     <row r="52" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="110"/>
+      <c r="A52" s="118"/>
       <c r="B52" s="31">
         <v>5</v>
       </c>
@@ -5103,10 +5095,10 @@
         <v/>
       </c>
       <c r="T52" s="41"/>
-      <c r="U52" s="116"/>
+      <c r="U52" s="104"/>
     </row>
     <row r="53" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="110"/>
+      <c r="A53" s="118"/>
       <c r="B53" s="31">
         <v>6</v>
       </c>
@@ -5178,10 +5170,10 @@
         <v/>
       </c>
       <c r="T53" s="41"/>
-      <c r="U53" s="116"/>
+      <c r="U53" s="104"/>
     </row>
     <row r="54" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="110"/>
+      <c r="A54" s="118"/>
       <c r="B54" s="31">
         <v>7</v>
       </c>
@@ -5248,10 +5240,10 @@
       <c r="R54" s="45"/>
       <c r="S54" s="46"/>
       <c r="T54" s="41"/>
-      <c r="U54" s="116"/>
+      <c r="U54" s="104"/>
     </row>
     <row r="55" spans="1:25" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="111"/>
+      <c r="A55" s="119"/>
       <c r="B55" s="31">
         <v>8</v>
       </c>
@@ -5318,7 +5310,7 @@
       <c r="R55" s="45"/>
       <c r="S55" s="46"/>
       <c r="T55" s="41"/>
-      <c r="U55" s="117"/>
+      <c r="U55" s="105"/>
     </row>
     <row r="56" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="58"/>
@@ -5383,17 +5375,17 @@
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($U$2,#REF!,0),1,2,"TUAN5")),"")</f>
         <v/>
       </c>
-      <c r="R56" s="118" t="s">
+      <c r="R56" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="S56" s="119"/>
-      <c r="T56" s="119"/>
-      <c r="U56" s="120"/>
+      <c r="S56" s="123"/>
+      <c r="T56" s="123"/>
+      <c r="U56" s="124"/>
       <c r="X56"/>
       <c r="Y56"/>
     </row>
     <row r="57" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="102" t="s">
+      <c r="A57" s="110" t="s">
         <v>5</v>
       </c>
       <c r="B57" s="53">
@@ -5459,13 +5451,13 @@
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($U$2,#REF!,0),1,2,"TUAN5")),"")</f>
         <v/>
       </c>
-      <c r="R57" s="121"/>
-      <c r="S57" s="122"/>
-      <c r="T57" s="122"/>
-      <c r="U57" s="123"/>
+      <c r="R57" s="125"/>
+      <c r="S57" s="126"/>
+      <c r="T57" s="126"/>
+      <c r="U57" s="127"/>
     </row>
     <row r="58" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="103"/>
+      <c r="A58" s="111"/>
       <c r="B58" s="53">
         <v>2</v>
       </c>
@@ -5532,13 +5524,13 @@
       <c r="R58" s="45"/>
       <c r="S58" s="46"/>
       <c r="T58" s="41"/>
-      <c r="U58" s="114">
+      <c r="U58" s="120">
         <f ca="1">SUM(U10+U20+U30+U40+U50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="103"/>
+      <c r="A59" s="111"/>
       <c r="B59" s="53">
         <v>3</v>
       </c>
@@ -5605,10 +5597,10 @@
       <c r="R59" s="45"/>
       <c r="S59" s="46"/>
       <c r="T59" s="41"/>
-      <c r="U59" s="114"/>
+      <c r="U59" s="120"/>
     </row>
     <row r="60" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="103"/>
+      <c r="A60" s="111"/>
       <c r="B60" s="53">
         <v>4</v>
       </c>
@@ -5675,10 +5667,10 @@
       <c r="R60" s="45"/>
       <c r="S60" s="46"/>
       <c r="T60" s="41"/>
-      <c r="U60" s="114"/>
+      <c r="U60" s="120"/>
     </row>
     <row r="61" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="103"/>
+      <c r="A61" s="111"/>
       <c r="B61" s="44"/>
       <c r="C61" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -5743,10 +5735,10 @@
       <c r="R61" s="45"/>
       <c r="S61" s="46"/>
       <c r="T61" s="41"/>
-      <c r="U61" s="114"/>
+      <c r="U61" s="120"/>
     </row>
     <row r="62" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="103"/>
+      <c r="A62" s="111"/>
       <c r="B62" s="53">
         <v>5</v>
       </c>
@@ -5813,10 +5805,10 @@
       <c r="R62" s="45"/>
       <c r="S62" s="46"/>
       <c r="T62" s="41"/>
-      <c r="U62" s="114"/>
+      <c r="U62" s="120"/>
     </row>
     <row r="63" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="103"/>
+      <c r="A63" s="111"/>
       <c r="B63" s="53">
         <v>6</v>
       </c>
@@ -5883,10 +5875,10 @@
       <c r="R63" s="45"/>
       <c r="S63" s="46"/>
       <c r="T63" s="41"/>
-      <c r="U63" s="114"/>
+      <c r="U63" s="120"/>
     </row>
     <row r="64" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="103"/>
+      <c r="A64" s="111"/>
       <c r="B64" s="53">
         <v>7</v>
       </c>
@@ -5953,10 +5945,10 @@
       <c r="R64" s="45"/>
       <c r="S64" s="46"/>
       <c r="T64" s="41"/>
-      <c r="U64" s="114"/>
+      <c r="U64" s="120"/>
     </row>
     <row r="65" spans="1:21" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="104"/>
+      <c r="A65" s="112"/>
       <c r="B65" s="53">
         <v>8</v>
       </c>
@@ -6023,7 +6015,7 @@
       <c r="R65" s="59"/>
       <c r="S65" s="50"/>
       <c r="T65" s="60"/>
-      <c r="U65" s="115"/>
+      <c r="U65" s="121"/>
     </row>
     <row r="66" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="61"/>
@@ -6044,24 +6036,24 @@
       <c r="H66" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I66" s="128" t="s">
+      <c r="I66" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="J66" s="129"/>
-      <c r="K66" s="130"/>
-      <c r="L66" s="131" t="s">
+      <c r="J66" s="91"/>
+      <c r="K66" s="92"/>
+      <c r="L66" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="M66" s="132"/>
-      <c r="N66" s="133"/>
+      <c r="M66" s="94"/>
+      <c r="N66" s="95"/>
       <c r="O66" s="69"/>
       <c r="P66" s="69"/>
       <c r="Q66" s="70"/>
-      <c r="R66" s="134" t="s">
+      <c r="R66" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="S66" s="135"/>
-      <c r="T66" s="136"/>
+      <c r="S66" s="97"/>
+      <c r="T66" s="98"/>
       <c r="U66" s="71"/>
     </row>
     <row r="67" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6088,57 +6080,57 @@
         <f ca="1">COUNTIF(C7:T65,"8*")</f>
         <v>0</v>
       </c>
-      <c r="I67" s="137">
+      <c r="I67" s="99">
         <f ca="1">COUNTIF(C7:T65,"9*")</f>
         <v>0</v>
       </c>
-      <c r="J67" s="138"/>
-      <c r="K67" s="139"/>
-      <c r="L67" s="137">
+      <c r="J67" s="100"/>
+      <c r="K67" s="101"/>
+      <c r="L67" s="99">
         <f ca="1">COUNTIF(C7:T65,"10*")+COUNTIF(C7:T65,"11*")</f>
         <v>0</v>
       </c>
-      <c r="M67" s="138"/>
-      <c r="N67" s="139"/>
-      <c r="O67" s="137"/>
-      <c r="P67" s="138"/>
-      <c r="Q67" s="139"/>
-      <c r="R67" s="137">
+      <c r="M67" s="100"/>
+      <c r="N67" s="101"/>
+      <c r="O67" s="99"/>
+      <c r="P67" s="100"/>
+      <c r="Q67" s="101"/>
+      <c r="R67" s="99">
         <f ca="1">COUNTIF(C7:T65,"12*")</f>
         <v>0</v>
       </c>
-      <c r="S67" s="138"/>
-      <c r="T67" s="139"/>
+      <c r="S67" s="100"/>
+      <c r="T67" s="101"/>
       <c r="U67" s="71"/>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="105" t="s">
+      <c r="A68" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="106"/>
-      <c r="C68" s="106"/>
-      <c r="D68" s="106"/>
-      <c r="E68" s="106"/>
-      <c r="F68" s="106"/>
-      <c r="G68" s="106" t="s">
+      <c r="B68" s="114"/>
+      <c r="C68" s="114"/>
+      <c r="D68" s="114"/>
+      <c r="E68" s="114"/>
+      <c r="F68" s="114"/>
+      <c r="G68" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="H68" s="106"/>
-      <c r="I68" s="106"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="107" t="s">
+      <c r="H68" s="114"/>
+      <c r="I68" s="114"/>
+      <c r="J68" s="114"/>
+      <c r="K68" s="114"/>
+      <c r="L68" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="M68" s="107"/>
-      <c r="N68" s="107"/>
-      <c r="O68" s="107"/>
-      <c r="P68" s="107"/>
-      <c r="Q68" s="107"/>
-      <c r="R68" s="107"/>
-      <c r="S68" s="107"/>
-      <c r="T68" s="107"/>
-      <c r="U68" s="108"/>
+      <c r="M68" s="115"/>
+      <c r="N68" s="115"/>
+      <c r="O68" s="115"/>
+      <c r="P68" s="115"/>
+      <c r="Q68" s="115"/>
+      <c r="R68" s="115"/>
+      <c r="S68" s="115"/>
+      <c r="T68" s="115"/>
+      <c r="U68" s="116"/>
     </row>
     <row r="69" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="76"/>
@@ -6168,33 +6160,31 @@
       <c r="D71" s="83"/>
       <c r="E71" s="83"/>
       <c r="F71" s="83"/>
-      <c r="G71" s="140" t="s">
+      <c r="G71" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="H71" s="140"/>
-      <c r="I71" s="140"/>
-      <c r="J71" s="140"/>
-      <c r="K71" s="140"/>
-      <c r="L71" s="140" t="s">
-        <v>45</v>
-      </c>
-      <c r="M71" s="140"/>
-      <c r="N71" s="140"/>
-      <c r="O71" s="140"/>
-      <c r="P71" s="140"/>
-      <c r="Q71" s="140"/>
-      <c r="R71" s="140"/>
-      <c r="S71" s="140"/>
-      <c r="T71" s="140"/>
-      <c r="U71" s="141"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="102"/>
+      <c r="J71" s="102"/>
+      <c r="K71" s="102"/>
+      <c r="L71" s="102"/>
+      <c r="M71" s="102"/>
+      <c r="N71" s="102"/>
+      <c r="O71" s="102"/>
+      <c r="P71" s="102"/>
+      <c r="Q71" s="102"/>
+      <c r="R71" s="102"/>
+      <c r="S71" s="102"/>
+      <c r="T71" s="102"/>
+      <c r="U71" s="103"/>
     </row>
     <row r="72" spans="1:21" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="126"/>
-      <c r="B72" s="127"/>
-      <c r="C72" s="127"/>
-      <c r="D72" s="127"/>
-      <c r="E72" s="127"/>
-      <c r="F72" s="127"/>
+      <c r="A72" s="88"/>
+      <c r="B72" s="89"/>
+      <c r="C72" s="89"/>
+      <c r="D72" s="89"/>
+      <c r="E72" s="89"/>
+      <c r="F72" s="89"/>
       <c r="G72" s="84"/>
       <c r="H72" s="85"/>
       <c r="I72" s="85"/>
@@ -6214,36 +6204,6 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="42">
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:N66"/>
-    <mergeCell ref="R66:T66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="L67:N67"/>
-    <mergeCell ref="O67:Q67"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="L71:U71"/>
-    <mergeCell ref="G71:K71"/>
-    <mergeCell ref="U10:U16"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="A37:A45"/>
-    <mergeCell ref="A27:A35"/>
-    <mergeCell ref="U20:U26"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="U30:U36"/>
-    <mergeCell ref="A7:A15"/>
-    <mergeCell ref="U40:U46"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="L68:U68"/>
-    <mergeCell ref="A47:A55"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="U58:U65"/>
-    <mergeCell ref="U50:U55"/>
-    <mergeCell ref="R56:U57"/>
-    <mergeCell ref="G68:K68"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A3:U3"/>
@@ -6256,8 +6216,38 @@
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="L68:U68"/>
+    <mergeCell ref="A47:A55"/>
+    <mergeCell ref="U47:U48"/>
+    <mergeCell ref="U58:U65"/>
+    <mergeCell ref="U50:U55"/>
+    <mergeCell ref="R56:U57"/>
+    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="U10:U16"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="U37:U38"/>
+    <mergeCell ref="A37:A45"/>
+    <mergeCell ref="A27:A35"/>
+    <mergeCell ref="U20:U26"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="U30:U36"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="U40:U46"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="R66:T66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="O67:Q67"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="L71:U71"/>
+    <mergeCell ref="G71:K71"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 N2:S2" xr:uid="{00DA29C0-4EEF-4ADD-985B-DBFA474DE47C}">
       <formula1>#REF!</formula1>
     </dataValidation>

--- a/BaoCaoMau.xlsx
+++ b/BaoCaoMau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AI\AI_giao_duc\Au-Viet-My\ChamCong_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B795F679-03C4-4622-A71A-CA0CBA295295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ADB076-C18B-434C-A7ED-D7B633A28E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,6 +1093,120 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1139,120 +1253,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1699,11 +1699,11 @@
       <c r="U1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="8"/>
@@ -1716,39 +1716,39 @@
         <v>23</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
       <c r="T2" s="10"/>
       <c r="U2" s="11"/>
     </row>
     <row r="3" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="130" t="s">
+      <c r="A3" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="131"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="131"/>
-      <c r="S3" s="131"/>
-      <c r="T3" s="131"/>
-      <c r="U3" s="132"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
+      <c r="S3" s="91"/>
+      <c r="T3" s="91"/>
+      <c r="U3" s="92"/>
     </row>
     <row r="4" spans="1:25" ht="15.4" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
@@ -1771,49 +1771,49 @@
         <v>8</v>
       </c>
       <c r="R4" s="16"/>
-      <c r="S4" s="139">
+      <c r="S4" s="99">
         <v>3</v>
       </c>
-      <c r="T4" s="139"/>
+      <c r="T4" s="99"/>
       <c r="U4" s="17"/>
       <c r="W4" s="18"/>
     </row>
     <row r="5" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135" t="s">
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135" t="s">
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135" t="s">
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
-      <c r="O5" s="135" t="s">
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="136" t="s">
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="137"/>
-      <c r="T5" s="137"/>
-      <c r="U5" s="138"/>
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="98"/>
       <c r="W5" s="19"/>
     </row>
     <row r="6" spans="1:25" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1877,7 +1877,7 @@
       <c r="W6" s="18"/>
     </row>
     <row r="7" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="125" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="31">
@@ -1956,7 +1956,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="109"/>
+      <c r="A8" s="125"/>
       <c r="B8" s="31">
         <v>2</v>
       </c>
@@ -2031,7 +2031,7 @@
       <c r="U8" s="42"/>
     </row>
     <row r="9" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="109"/>
+      <c r="A9" s="125"/>
       <c r="B9" s="31">
         <v>3</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="109"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="31">
         <v>4</v>
       </c>
@@ -2180,13 +2180,13 @@
         <v/>
       </c>
       <c r="T10" s="41"/>
-      <c r="U10" s="104">
+      <c r="U10" s="116">
         <f ca="1">SUM(S7:S13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="109"/>
+      <c r="A11" s="125"/>
       <c r="B11" s="44"/>
       <c r="C11" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -2256,10 +2256,10 @@
         <v/>
       </c>
       <c r="T11" s="41"/>
-      <c r="U11" s="104"/>
+      <c r="U11" s="116"/>
     </row>
     <row r="12" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="109"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="31">
         <v>5</v>
       </c>
@@ -2331,10 +2331,10 @@
         <v/>
       </c>
       <c r="T12" s="41"/>
-      <c r="U12" s="104"/>
+      <c r="U12" s="116"/>
     </row>
     <row r="13" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="109"/>
+      <c r="A13" s="125"/>
       <c r="B13" s="31">
         <v>6</v>
       </c>
@@ -2406,10 +2406,10 @@
         <v/>
       </c>
       <c r="T13" s="41"/>
-      <c r="U13" s="104"/>
+      <c r="U13" s="116"/>
     </row>
     <row r="14" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="109"/>
+      <c r="A14" s="125"/>
       <c r="B14" s="31">
         <v>7</v>
       </c>
@@ -2473,10 +2473,10 @@
       <c r="R14" s="45"/>
       <c r="S14" s="46"/>
       <c r="T14" s="41"/>
-      <c r="U14" s="104"/>
+      <c r="U14" s="116"/>
     </row>
     <row r="15" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="109"/>
+      <c r="A15" s="125"/>
       <c r="B15" s="31">
         <v>8</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="R15" s="45"/>
       <c r="S15" s="46"/>
       <c r="T15" s="41"/>
-      <c r="U15" s="104"/>
+      <c r="U15" s="116"/>
     </row>
     <row r="16" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="47"/>
@@ -2605,13 +2605,13 @@
       <c r="R16" s="49"/>
       <c r="S16" s="50"/>
       <c r="T16" s="51"/>
-      <c r="U16" s="105"/>
+      <c r="U16" s="117"/>
       <c r="V16"/>
       <c r="X16"/>
       <c r="Y16"/>
     </row>
     <row r="17" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="124" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="53">
@@ -2682,12 +2682,12 @@
         <v/>
       </c>
       <c r="T17" s="37"/>
-      <c r="U17" s="106" t="s">
+      <c r="U17" s="112" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="108"/>
+      <c r="A18" s="124"/>
       <c r="B18" s="53">
         <v>2</v>
       </c>
@@ -2750,10 +2750,10 @@
         <v/>
       </c>
       <c r="T18" s="41"/>
-      <c r="U18" s="107"/>
+      <c r="U18" s="113"/>
     </row>
     <row r="19" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="108"/>
+      <c r="A19" s="124"/>
       <c r="B19" s="53">
         <v>3</v>
       </c>
@@ -2821,7 +2821,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="108"/>
+      <c r="A20" s="124"/>
       <c r="B20" s="53">
         <v>4</v>
       </c>
@@ -2884,13 +2884,13 @@
         <v/>
       </c>
       <c r="T20" s="41"/>
-      <c r="U20" s="104">
+      <c r="U20" s="116">
         <f ca="1">SUM(S17:S23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="108"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="55"/>
       <c r="C21" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -2951,10 +2951,10 @@
         <v/>
       </c>
       <c r="T21" s="41"/>
-      <c r="U21" s="104"/>
+      <c r="U21" s="116"/>
     </row>
     <row r="22" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
+      <c r="A22" s="124"/>
       <c r="B22" s="53">
         <v>5</v>
       </c>
@@ -3017,10 +3017,10 @@
         <v/>
       </c>
       <c r="T22" s="41"/>
-      <c r="U22" s="104"/>
+      <c r="U22" s="116"/>
     </row>
     <row r="23" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="108"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="53">
         <v>6</v>
       </c>
@@ -3083,10 +3083,10 @@
         <v/>
       </c>
       <c r="T23" s="41"/>
-      <c r="U23" s="104"/>
+      <c r="U23" s="116"/>
     </row>
     <row r="24" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="108"/>
+      <c r="A24" s="124"/>
       <c r="B24" s="53">
         <v>7</v>
       </c>
@@ -3144,10 +3144,10 @@
       <c r="R24" s="45"/>
       <c r="S24" s="46"/>
       <c r="T24" s="41"/>
-      <c r="U24" s="104"/>
+      <c r="U24" s="116"/>
     </row>
     <row r="25" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="124"/>
       <c r="B25" s="53">
         <v>8</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="R25" s="45"/>
       <c r="S25" s="46"/>
       <c r="T25" s="41"/>
-      <c r="U25" s="104"/>
+      <c r="U25" s="116"/>
     </row>
     <row r="26" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="47"/>
@@ -3264,12 +3264,12 @@
       <c r="R26" s="49"/>
       <c r="S26" s="50"/>
       <c r="T26" s="51"/>
-      <c r="U26" s="105"/>
+      <c r="U26" s="117"/>
       <c r="X26"/>
       <c r="Y26"/>
     </row>
     <row r="27" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="125" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="31">
@@ -3334,12 +3334,12 @@
         <v/>
       </c>
       <c r="T27" s="37"/>
-      <c r="U27" s="106" t="s">
+      <c r="U27" s="112" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109"/>
+      <c r="A28" s="125"/>
       <c r="B28" s="31">
         <v>2</v>
       </c>
@@ -3402,10 +3402,10 @@
         <v/>
       </c>
       <c r="T28" s="41"/>
-      <c r="U28" s="107"/>
+      <c r="U28" s="113"/>
     </row>
     <row r="29" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="109"/>
+      <c r="A29" s="125"/>
       <c r="B29" s="31">
         <v>3</v>
       </c>
@@ -3473,7 +3473,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="109"/>
+      <c r="A30" s="125"/>
       <c r="B30" s="31">
         <v>4</v>
       </c>
@@ -3536,13 +3536,13 @@
         <v/>
       </c>
       <c r="T30" s="41"/>
-      <c r="U30" s="104">
+      <c r="U30" s="116">
         <f ca="1">SUM(S27:S33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="109"/>
+      <c r="A31" s="125"/>
       <c r="B31" s="44"/>
       <c r="C31" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -3603,10 +3603,10 @@
         <v/>
       </c>
       <c r="T31" s="41"/>
-      <c r="U31" s="104"/>
+      <c r="U31" s="116"/>
     </row>
     <row r="32" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="109"/>
+      <c r="A32" s="125"/>
       <c r="B32" s="31">
         <v>5</v>
       </c>
@@ -3669,10 +3669,10 @@
         <v/>
       </c>
       <c r="T32" s="41"/>
-      <c r="U32" s="104"/>
+      <c r="U32" s="116"/>
     </row>
     <row r="33" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="109"/>
+      <c r="A33" s="125"/>
       <c r="B33" s="31">
         <v>6</v>
       </c>
@@ -3735,10 +3735,10 @@
         <v/>
       </c>
       <c r="T33" s="41"/>
-      <c r="U33" s="104"/>
+      <c r="U33" s="116"/>
     </row>
     <row r="34" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="109"/>
+      <c r="A34" s="125"/>
       <c r="B34" s="31">
         <v>7</v>
       </c>
@@ -3796,10 +3796,10 @@
       <c r="R34" s="45"/>
       <c r="S34" s="46"/>
       <c r="T34" s="41"/>
-      <c r="U34" s="104"/>
+      <c r="U34" s="116"/>
     </row>
     <row r="35" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="109"/>
+      <c r="A35" s="125"/>
       <c r="B35" s="31">
         <v>8</v>
       </c>
@@ -3857,7 +3857,7 @@
       <c r="R35" s="45"/>
       <c r="S35" s="46"/>
       <c r="T35" s="41"/>
-      <c r="U35" s="104"/>
+      <c r="U35" s="116"/>
     </row>
     <row r="36" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="47"/>
@@ -3916,12 +3916,12 @@
       <c r="R36" s="49"/>
       <c r="S36" s="50"/>
       <c r="T36" s="51"/>
-      <c r="U36" s="105"/>
+      <c r="U36" s="117"/>
       <c r="X36"/>
       <c r="Y36"/>
     </row>
     <row r="37" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="108" t="s">
+      <c r="A37" s="124" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="53">
@@ -3986,12 +3986,12 @@
         <v/>
       </c>
       <c r="T37" s="37"/>
-      <c r="U37" s="106" t="s">
+      <c r="U37" s="112" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="108"/>
+      <c r="A38" s="124"/>
       <c r="B38" s="53">
         <v>2</v>
       </c>
@@ -4054,10 +4054,10 @@
         <v/>
       </c>
       <c r="T38" s="41"/>
-      <c r="U38" s="107"/>
+      <c r="U38" s="113"/>
     </row>
     <row r="39" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="108"/>
+      <c r="A39" s="124"/>
       <c r="B39" s="53">
         <v>3</v>
       </c>
@@ -4134,7 +4134,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="108"/>
+      <c r="A40" s="124"/>
       <c r="B40" s="53">
         <v>4</v>
       </c>
@@ -4203,13 +4203,13 @@
         <v/>
       </c>
       <c r="T40" s="41"/>
-      <c r="U40" s="104">
+      <c r="U40" s="116">
         <f ca="1">SUM(S37:S43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="124"/>
       <c r="B41" s="56"/>
       <c r="C41" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -4279,10 +4279,10 @@
         <v/>
       </c>
       <c r="T41" s="41"/>
-      <c r="U41" s="104"/>
+      <c r="U41" s="116"/>
     </row>
     <row r="42" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="108"/>
+      <c r="A42" s="124"/>
       <c r="B42" s="53">
         <v>5</v>
       </c>
@@ -4354,10 +4354,10 @@
         <v/>
       </c>
       <c r="T42" s="41"/>
-      <c r="U42" s="104"/>
+      <c r="U42" s="116"/>
     </row>
     <row r="43" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="108"/>
+      <c r="A43" s="124"/>
       <c r="B43" s="53">
         <v>6</v>
       </c>
@@ -4429,10 +4429,10 @@
         <v/>
       </c>
       <c r="T43" s="41"/>
-      <c r="U43" s="104"/>
+      <c r="U43" s="116"/>
     </row>
     <row r="44" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="108"/>
+      <c r="A44" s="124"/>
       <c r="B44" s="53">
         <v>7</v>
       </c>
@@ -4499,10 +4499,10 @@
       <c r="R44" s="45"/>
       <c r="S44" s="46"/>
       <c r="T44" s="41"/>
-      <c r="U44" s="104"/>
+      <c r="U44" s="116"/>
     </row>
     <row r="45" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="108"/>
+      <c r="A45" s="124"/>
       <c r="B45" s="53">
         <v>8</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="R45" s="45"/>
       <c r="S45" s="46"/>
       <c r="T45" s="41"/>
-      <c r="U45" s="104"/>
+      <c r="U45" s="116"/>
     </row>
     <row r="46" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="57"/>
@@ -4637,12 +4637,12 @@
       <c r="R46" s="49"/>
       <c r="S46" s="50"/>
       <c r="T46" s="51"/>
-      <c r="U46" s="105"/>
+      <c r="U46" s="117"/>
       <c r="X46"/>
       <c r="Y46"/>
     </row>
     <row r="47" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="117" t="s">
+      <c r="A47" s="109" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="31">
@@ -4716,12 +4716,12 @@
         <v/>
       </c>
       <c r="T47" s="37"/>
-      <c r="U47" s="106" t="s">
+      <c r="U47" s="112" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="118"/>
+      <c r="A48" s="110"/>
       <c r="B48" s="31">
         <v>2</v>
       </c>
@@ -4793,10 +4793,10 @@
         <v/>
       </c>
       <c r="T48" s="41"/>
-      <c r="U48" s="107"/>
+      <c r="U48" s="113"/>
     </row>
     <row r="49" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="118"/>
+      <c r="A49" s="110"/>
       <c r="B49" s="31">
         <v>3</v>
       </c>
@@ -4873,7 +4873,7 @@
       </c>
     </row>
     <row r="50" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="118"/>
+      <c r="A50" s="110"/>
       <c r="B50" s="31">
         <v>4</v>
       </c>
@@ -4945,12 +4945,13 @@
         <v/>
       </c>
       <c r="T50" s="41"/>
-      <c r="U50" s="104">
+      <c r="U50" s="116">
+        <f ca="1">SUM(S47:S53)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="118"/>
+      <c r="A51" s="110"/>
       <c r="B51" s="44"/>
       <c r="C51" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -5020,10 +5021,10 @@
         <v/>
       </c>
       <c r="T51" s="41"/>
-      <c r="U51" s="104"/>
+      <c r="U51" s="116"/>
     </row>
     <row r="52" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="118"/>
+      <c r="A52" s="110"/>
       <c r="B52" s="31">
         <v>5</v>
       </c>
@@ -5095,10 +5096,10 @@
         <v/>
       </c>
       <c r="T52" s="41"/>
-      <c r="U52" s="104"/>
+      <c r="U52" s="116"/>
     </row>
     <row r="53" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="118"/>
+      <c r="A53" s="110"/>
       <c r="B53" s="31">
         <v>6</v>
       </c>
@@ -5165,15 +5166,12 @@
       <c r="R53" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="S53" s="40" t="str">
-        <f ca="1">IF(COUNTIF(O7:Q64,"KH*")=0,"",COUNTIF(O7:Q64,"KH*"))</f>
-        <v/>
-      </c>
+      <c r="S53" s="40"/>
       <c r="T53" s="41"/>
-      <c r="U53" s="104"/>
+      <c r="U53" s="116"/>
     </row>
     <row r="54" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="118"/>
+      <c r="A54" s="110"/>
       <c r="B54" s="31">
         <v>7</v>
       </c>
@@ -5240,10 +5238,10 @@
       <c r="R54" s="45"/>
       <c r="S54" s="46"/>
       <c r="T54" s="41"/>
-      <c r="U54" s="104"/>
+      <c r="U54" s="116"/>
     </row>
     <row r="55" spans="1:25" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="119"/>
+      <c r="A55" s="111"/>
       <c r="B55" s="31">
         <v>8</v>
       </c>
@@ -5310,7 +5308,7 @@
       <c r="R55" s="45"/>
       <c r="S55" s="46"/>
       <c r="T55" s="41"/>
-      <c r="U55" s="105"/>
+      <c r="U55" s="117"/>
     </row>
     <row r="56" spans="1:25" s="52" customFormat="1" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="58"/>
@@ -5375,17 +5373,17 @@
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($U$2,#REF!,0),1,2,"TUAN5")),"")</f>
         <v/>
       </c>
-      <c r="R56" s="122" t="s">
+      <c r="R56" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="S56" s="123"/>
-      <c r="T56" s="123"/>
-      <c r="U56" s="124"/>
+      <c r="S56" s="119"/>
+      <c r="T56" s="119"/>
+      <c r="U56" s="120"/>
       <c r="X56"/>
       <c r="Y56"/>
     </row>
     <row r="57" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="110" t="s">
+      <c r="A57" s="102" t="s">
         <v>5</v>
       </c>
       <c r="B57" s="53">
@@ -5451,13 +5449,13 @@
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($U$2,#REF!,0),1,2,"TUAN5")),"")</f>
         <v/>
       </c>
-      <c r="R57" s="125"/>
-      <c r="S57" s="126"/>
-      <c r="T57" s="126"/>
-      <c r="U57" s="127"/>
+      <c r="R57" s="121"/>
+      <c r="S57" s="122"/>
+      <c r="T57" s="122"/>
+      <c r="U57" s="123"/>
     </row>
     <row r="58" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="111"/>
+      <c r="A58" s="103"/>
       <c r="B58" s="53">
         <v>2</v>
       </c>
@@ -5524,13 +5522,13 @@
       <c r="R58" s="45"/>
       <c r="S58" s="46"/>
       <c r="T58" s="41"/>
-      <c r="U58" s="120">
+      <c r="U58" s="114">
         <f ca="1">SUM(U10+U20+U30+U40+U50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="111"/>
+      <c r="A59" s="103"/>
       <c r="B59" s="53">
         <v>3</v>
       </c>
@@ -5597,10 +5595,10 @@
       <c r="R59" s="45"/>
       <c r="S59" s="46"/>
       <c r="T59" s="41"/>
-      <c r="U59" s="120"/>
+      <c r="U59" s="114"/>
     </row>
     <row r="60" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="111"/>
+      <c r="A60" s="103"/>
       <c r="B60" s="53">
         <v>4</v>
       </c>
@@ -5667,10 +5665,10 @@
       <c r="R60" s="45"/>
       <c r="S60" s="46"/>
       <c r="T60" s="41"/>
-      <c r="U60" s="120"/>
+      <c r="U60" s="114"/>
     </row>
     <row r="61" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="111"/>
+      <c r="A61" s="103"/>
       <c r="B61" s="44"/>
       <c r="C61" s="32" t="str">
         <f ca="1">IFERROR(INDIRECT(ADDRESS(2,MATCH($Q$2,#REF!,0),1,2,"TUAN1")),"")</f>
@@ -5735,10 +5733,10 @@
       <c r="R61" s="45"/>
       <c r="S61" s="46"/>
       <c r="T61" s="41"/>
-      <c r="U61" s="120"/>
+      <c r="U61" s="114"/>
     </row>
     <row r="62" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="111"/>
+      <c r="A62" s="103"/>
       <c r="B62" s="53">
         <v>5</v>
       </c>
@@ -5805,10 +5803,10 @@
       <c r="R62" s="45"/>
       <c r="S62" s="46"/>
       <c r="T62" s="41"/>
-      <c r="U62" s="120"/>
+      <c r="U62" s="114"/>
     </row>
     <row r="63" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="111"/>
+      <c r="A63" s="103"/>
       <c r="B63" s="53">
         <v>6</v>
       </c>
@@ -5875,10 +5873,10 @@
       <c r="R63" s="45"/>
       <c r="S63" s="46"/>
       <c r="T63" s="41"/>
-      <c r="U63" s="120"/>
+      <c r="U63" s="114"/>
     </row>
     <row r="64" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="111"/>
+      <c r="A64" s="103"/>
       <c r="B64" s="53">
         <v>7</v>
       </c>
@@ -5945,10 +5943,10 @@
       <c r="R64" s="45"/>
       <c r="S64" s="46"/>
       <c r="T64" s="41"/>
-      <c r="U64" s="120"/>
+      <c r="U64" s="114"/>
     </row>
     <row r="65" spans="1:21" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="112"/>
+      <c r="A65" s="104"/>
       <c r="B65" s="53">
         <v>8</v>
       </c>
@@ -6015,7 +6013,7 @@
       <c r="R65" s="59"/>
       <c r="S65" s="50"/>
       <c r="T65" s="60"/>
-      <c r="U65" s="121"/>
+      <c r="U65" s="115"/>
     </row>
     <row r="66" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="61"/>
@@ -6036,24 +6034,24 @@
       <c r="H66" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I66" s="90" t="s">
+      <c r="I66" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="J66" s="91"/>
-      <c r="K66" s="92"/>
-      <c r="L66" s="93" t="s">
+      <c r="J66" s="129"/>
+      <c r="K66" s="130"/>
+      <c r="L66" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="M66" s="94"/>
-      <c r="N66" s="95"/>
+      <c r="M66" s="132"/>
+      <c r="N66" s="133"/>
       <c r="O66" s="69"/>
       <c r="P66" s="69"/>
       <c r="Q66" s="70"/>
-      <c r="R66" s="96" t="s">
+      <c r="R66" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="S66" s="97"/>
-      <c r="T66" s="98"/>
+      <c r="S66" s="135"/>
+      <c r="T66" s="136"/>
       <c r="U66" s="71"/>
     </row>
     <row r="67" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6080,57 +6078,57 @@
         <f ca="1">COUNTIF(C7:T65,"8*")</f>
         <v>0</v>
       </c>
-      <c r="I67" s="99">
+      <c r="I67" s="137">
         <f ca="1">COUNTIF(C7:T65,"9*")</f>
         <v>0</v>
       </c>
-      <c r="J67" s="100"/>
-      <c r="K67" s="101"/>
-      <c r="L67" s="99">
+      <c r="J67" s="138"/>
+      <c r="K67" s="139"/>
+      <c r="L67" s="137">
         <f ca="1">COUNTIF(C7:T65,"10*")+COUNTIF(C7:T65,"11*")</f>
         <v>0</v>
       </c>
-      <c r="M67" s="100"/>
-      <c r="N67" s="101"/>
-      <c r="O67" s="99"/>
-      <c r="P67" s="100"/>
-      <c r="Q67" s="101"/>
-      <c r="R67" s="99">
+      <c r="M67" s="138"/>
+      <c r="N67" s="139"/>
+      <c r="O67" s="137"/>
+      <c r="P67" s="138"/>
+      <c r="Q67" s="139"/>
+      <c r="R67" s="137">
         <f ca="1">COUNTIF(C7:T65,"12*")</f>
         <v>0</v>
       </c>
-      <c r="S67" s="100"/>
-      <c r="T67" s="101"/>
+      <c r="S67" s="138"/>
+      <c r="T67" s="139"/>
       <c r="U67" s="71"/>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="113" t="s">
+      <c r="A68" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="114"/>
-      <c r="C68" s="114"/>
-      <c r="D68" s="114"/>
-      <c r="E68" s="114"/>
-      <c r="F68" s="114"/>
-      <c r="G68" s="114" t="s">
+      <c r="B68" s="106"/>
+      <c r="C68" s="106"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="106"/>
+      <c r="G68" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="H68" s="114"/>
-      <c r="I68" s="114"/>
-      <c r="J68" s="114"/>
-      <c r="K68" s="114"/>
-      <c r="L68" s="115" t="s">
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
+      <c r="J68" s="106"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="M68" s="115"/>
-      <c r="N68" s="115"/>
-      <c r="O68" s="115"/>
-      <c r="P68" s="115"/>
-      <c r="Q68" s="115"/>
-      <c r="R68" s="115"/>
-      <c r="S68" s="115"/>
-      <c r="T68" s="115"/>
-      <c r="U68" s="116"/>
+      <c r="M68" s="107"/>
+      <c r="N68" s="107"/>
+      <c r="O68" s="107"/>
+      <c r="P68" s="107"/>
+      <c r="Q68" s="107"/>
+      <c r="R68" s="107"/>
+      <c r="S68" s="107"/>
+      <c r="T68" s="107"/>
+      <c r="U68" s="108"/>
     </row>
     <row r="69" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="76"/>
@@ -6160,31 +6158,31 @@
       <c r="D71" s="83"/>
       <c r="E71" s="83"/>
       <c r="F71" s="83"/>
-      <c r="G71" s="102" t="s">
+      <c r="G71" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="H71" s="102"/>
-      <c r="I71" s="102"/>
-      <c r="J71" s="102"/>
-      <c r="K71" s="102"/>
-      <c r="L71" s="102"/>
-      <c r="M71" s="102"/>
-      <c r="N71" s="102"/>
-      <c r="O71" s="102"/>
-      <c r="P71" s="102"/>
-      <c r="Q71" s="102"/>
-      <c r="R71" s="102"/>
-      <c r="S71" s="102"/>
-      <c r="T71" s="102"/>
-      <c r="U71" s="103"/>
+      <c r="H71" s="140"/>
+      <c r="I71" s="140"/>
+      <c r="J71" s="140"/>
+      <c r="K71" s="140"/>
+      <c r="L71" s="140"/>
+      <c r="M71" s="140"/>
+      <c r="N71" s="140"/>
+      <c r="O71" s="140"/>
+      <c r="P71" s="140"/>
+      <c r="Q71" s="140"/>
+      <c r="R71" s="140"/>
+      <c r="S71" s="140"/>
+      <c r="T71" s="140"/>
+      <c r="U71" s="141"/>
     </row>
     <row r="72" spans="1:21" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="88"/>
-      <c r="B72" s="89"/>
-      <c r="C72" s="89"/>
-      <c r="D72" s="89"/>
-      <c r="E72" s="89"/>
-      <c r="F72" s="89"/>
+      <c r="A72" s="126"/>
+      <c r="B72" s="127"/>
+      <c r="C72" s="127"/>
+      <c r="D72" s="127"/>
+      <c r="E72" s="127"/>
+      <c r="F72" s="127"/>
       <c r="G72" s="84"/>
       <c r="H72" s="85"/>
       <c r="I72" s="85"/>
@@ -6204,6 +6202,36 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="42">
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="R66:T66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="O67:Q67"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="L71:U71"/>
+    <mergeCell ref="G71:K71"/>
+    <mergeCell ref="U10:U16"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="U37:U38"/>
+    <mergeCell ref="A37:A45"/>
+    <mergeCell ref="A27:A35"/>
+    <mergeCell ref="U20:U26"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="U30:U36"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="U40:U46"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="L68:U68"/>
+    <mergeCell ref="A47:A55"/>
+    <mergeCell ref="U47:U48"/>
+    <mergeCell ref="U58:U65"/>
+    <mergeCell ref="U50:U55"/>
+    <mergeCell ref="R56:U57"/>
+    <mergeCell ref="G68:K68"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A3:U3"/>
@@ -6216,36 +6244,6 @@
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="L68:U68"/>
-    <mergeCell ref="A47:A55"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="U58:U65"/>
-    <mergeCell ref="U50:U55"/>
-    <mergeCell ref="R56:U57"/>
-    <mergeCell ref="G68:K68"/>
-    <mergeCell ref="U10:U16"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="A37:A45"/>
-    <mergeCell ref="A27:A35"/>
-    <mergeCell ref="U20:U26"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="U30:U36"/>
-    <mergeCell ref="A7:A15"/>
-    <mergeCell ref="U40:U46"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:N66"/>
-    <mergeCell ref="R66:T66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="L67:N67"/>
-    <mergeCell ref="O67:Q67"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="L71:U71"/>
-    <mergeCell ref="G71:K71"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 N2:S2" xr:uid="{00DA29C0-4EEF-4ADD-985B-DBFA474DE47C}">

--- a/BaoCaoMau.xlsx
+++ b/BaoCaoMau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AI\AI_giao_duc\Au-Viet-My\ChamCong_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1E7855-EBB5-4024-80BB-27DC7E6E4F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CF41EA-5026-4ACE-90BF-99C3FFE59FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="3615" windowWidth="16875" windowHeight="10522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FILE IN" sheetId="4" r:id="rId1"/>
@@ -1109,31 +1109,64 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1184,12 +1217,6 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,59 +1235,32 @@
     <xf numFmtId="0" fontId="20" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1706,11 +1706,11 @@
       <c r="U1" s="6"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="8"/>
@@ -1731,29 +1731,29 @@
       <c r="U2" s="80"/>
     </row>
     <row r="3" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="94"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="95"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="136"/>
+      <c r="U3" s="137"/>
     </row>
     <row r="4" spans="1:25" ht="15.4" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
@@ -1782,41 +1782,41 @@
       <c r="W4" s="13"/>
     </row>
     <row r="5" spans="1:25" ht="15" x14ac:dyDescent="0.35">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98" t="s">
+      <c r="B5" s="139"/>
+      <c r="C5" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98" t="s">
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98" t="s">
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98" t="s">
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98" t="s">
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="99" t="s">
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="101"/>
+      <c r="S5" s="142"/>
+      <c r="T5" s="142"/>
+      <c r="U5" s="143"/>
       <c r="W5" s="14"/>
     </row>
     <row r="6" spans="1:25" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1850,7 +1850,7 @@
       <c r="W6" s="13"/>
     </row>
     <row r="7" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="112" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="26">
@@ -1884,7 +1884,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="127"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="26">
         <v>2</v>
       </c>
@@ -1914,7 +1914,7 @@
       <c r="U8" s="37"/>
     </row>
     <row r="9" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="127"/>
+      <c r="A9" s="112"/>
       <c r="B9" s="26">
         <v>3</v>
       </c>
@@ -1946,7 +1946,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="127"/>
+      <c r="A10" s="112"/>
       <c r="B10" s="26">
         <v>4</v>
       </c>
@@ -1973,13 +1973,13 @@
         <v/>
       </c>
       <c r="T10" s="36"/>
-      <c r="U10" s="118">
+      <c r="U10" s="109">
         <f>SUM(S7:S13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="127"/>
+      <c r="A11" s="112"/>
       <c r="B11" s="39"/>
       <c r="C11" s="85"/>
       <c r="D11" s="86"/>
@@ -2004,10 +2004,10 @@
         <v/>
       </c>
       <c r="T11" s="36"/>
-      <c r="U11" s="118"/>
+      <c r="U11" s="109"/>
     </row>
     <row r="12" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="127"/>
+      <c r="A12" s="112"/>
       <c r="B12" s="26">
         <v>5</v>
       </c>
@@ -2034,10 +2034,10 @@
         <v/>
       </c>
       <c r="T12" s="36"/>
-      <c r="U12" s="118"/>
+      <c r="U12" s="109"/>
     </row>
     <row r="13" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="127"/>
+      <c r="A13" s="112"/>
       <c r="B13" s="26">
         <v>6</v>
       </c>
@@ -2060,14 +2060,14 @@
         <v>35</v>
       </c>
       <c r="S13" s="35" t="str">
-        <f>IF(COUNTIF(C7:E65,"KH*")=0,"",COUNTIF(C7:E65,"KH*"))</f>
+        <f>IF(COUNTIF(C7:E65,"12*")=0,"",COUNTIF(C7:E65,"12*"))</f>
         <v/>
       </c>
       <c r="T13" s="36"/>
-      <c r="U13" s="118"/>
+      <c r="U13" s="109"/>
     </row>
     <row r="14" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="127"/>
+      <c r="A14" s="112"/>
       <c r="B14" s="26">
         <v>7</v>
       </c>
@@ -2089,10 +2089,10 @@
       <c r="R14" s="40"/>
       <c r="S14" s="41"/>
       <c r="T14" s="36"/>
-      <c r="U14" s="118"/>
+      <c r="U14" s="109"/>
     </row>
     <row r="15" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="127"/>
+      <c r="A15" s="112"/>
       <c r="B15" s="26">
         <v>8</v>
       </c>
@@ -2114,7 +2114,7 @@
       <c r="R15" s="40"/>
       <c r="S15" s="41"/>
       <c r="T15" s="36"/>
-      <c r="U15" s="118"/>
+      <c r="U15" s="109"/>
     </row>
     <row r="16" spans="1:25" s="45" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="81"/>
@@ -2137,13 +2137,13 @@
       <c r="R16" s="42"/>
       <c r="S16" s="43"/>
       <c r="T16" s="44"/>
-      <c r="U16" s="119"/>
+      <c r="U16" s="110"/>
       <c r="V16"/>
       <c r="X16"/>
       <c r="Y16"/>
     </row>
     <row r="17" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="111" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="46">
@@ -2172,12 +2172,12 @@
         <v/>
       </c>
       <c r="T17" s="32"/>
-      <c r="U17" s="114" t="s">
+      <c r="U17" s="125" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="126"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="46">
         <v>2</v>
       </c>
@@ -2204,10 +2204,10 @@
         <v/>
       </c>
       <c r="T18" s="36"/>
-      <c r="U18" s="115"/>
+      <c r="U18" s="126"/>
     </row>
     <row r="19" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="126"/>
+      <c r="A19" s="111"/>
       <c r="B19" s="46">
         <v>3</v>
       </c>
@@ -2239,7 +2239,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="126"/>
+      <c r="A20" s="111"/>
       <c r="B20" s="46">
         <v>4</v>
       </c>
@@ -2266,13 +2266,13 @@
         <v/>
       </c>
       <c r="T20" s="36"/>
-      <c r="U20" s="118">
+      <c r="U20" s="109">
         <f>SUM(S17:S23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="126"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="83"/>
       <c r="C21" s="83"/>
       <c r="D21" s="83"/>
@@ -2297,10 +2297,10 @@
         <v/>
       </c>
       <c r="T21" s="36"/>
-      <c r="U21" s="118"/>
+      <c r="U21" s="109"/>
     </row>
     <row r="22" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="126"/>
+      <c r="A22" s="111"/>
       <c r="B22" s="46">
         <v>5</v>
       </c>
@@ -2327,10 +2327,10 @@
         <v/>
       </c>
       <c r="T22" s="36"/>
-      <c r="U22" s="118"/>
+      <c r="U22" s="109"/>
     </row>
     <row r="23" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="126"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="46">
         <v>6</v>
       </c>
@@ -2353,14 +2353,14 @@
         <v>35</v>
       </c>
       <c r="S23" s="35" t="str">
-        <f>IF(COUNTIF(F7:H65,"KH*")=0,"",COUNTIF(F7:H65,"KH*"))</f>
+        <f>IF(COUNTIF(F7:H65,"12*")=0,"",COUNTIF(F7:H65,"12*"))</f>
         <v/>
       </c>
       <c r="T23" s="36"/>
-      <c r="U23" s="118"/>
+      <c r="U23" s="109"/>
     </row>
     <row r="24" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="126"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="46">
         <v>7</v>
       </c>
@@ -2382,10 +2382,10 @@
       <c r="R24" s="40"/>
       <c r="S24" s="41"/>
       <c r="T24" s="36"/>
-      <c r="U24" s="118"/>
+      <c r="U24" s="109"/>
     </row>
     <row r="25" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="126"/>
+      <c r="A25" s="111"/>
       <c r="B25" s="46">
         <v>8</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="R25" s="40"/>
       <c r="S25" s="41"/>
       <c r="T25" s="36"/>
-      <c r="U25" s="118"/>
+      <c r="U25" s="109"/>
     </row>
     <row r="26" spans="1:25" s="45" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="81"/>
@@ -2430,12 +2430,12 @@
       <c r="R26" s="42"/>
       <c r="S26" s="43"/>
       <c r="T26" s="44"/>
-      <c r="U26" s="119"/>
+      <c r="U26" s="110"/>
       <c r="X26"/>
       <c r="Y26"/>
     </row>
     <row r="27" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="127" t="s">
+      <c r="A27" s="112" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="26">
@@ -2464,12 +2464,12 @@
         <v/>
       </c>
       <c r="T27" s="32"/>
-      <c r="U27" s="114" t="s">
+      <c r="U27" s="125" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="127"/>
+      <c r="A28" s="112"/>
       <c r="B28" s="26">
         <v>2</v>
       </c>
@@ -2496,10 +2496,10 @@
         <v/>
       </c>
       <c r="T28" s="36"/>
-      <c r="U28" s="115"/>
+      <c r="U28" s="126"/>
     </row>
     <row r="29" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="127"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="26">
         <v>3</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="127"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="26">
         <v>4</v>
       </c>
@@ -2558,13 +2558,13 @@
         <v/>
       </c>
       <c r="T30" s="36"/>
-      <c r="U30" s="118">
+      <c r="U30" s="109">
         <f>SUM(S27:S33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="127"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="83"/>
       <c r="C31" s="83"/>
       <c r="D31" s="83"/>
@@ -2589,10 +2589,10 @@
         <v/>
       </c>
       <c r="T31" s="36"/>
-      <c r="U31" s="118"/>
+      <c r="U31" s="109"/>
     </row>
     <row r="32" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="127"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="26">
         <v>5</v>
       </c>
@@ -2619,10 +2619,10 @@
         <v/>
       </c>
       <c r="T32" s="36"/>
-      <c r="U32" s="118"/>
+      <c r="U32" s="109"/>
     </row>
     <row r="33" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="127"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="26">
         <v>6</v>
       </c>
@@ -2645,14 +2645,14 @@
         <v>35</v>
       </c>
       <c r="S33" s="35" t="str">
-        <f>IF(COUNTIF(I7:K65,"KH*")=0,"",COUNTIF(I7:K65,"KH*"))</f>
+        <f>IF(COUNTIF(I7:K65,"12*")=0,"",COUNTIF(I7:K65,"12*"))</f>
         <v/>
       </c>
       <c r="T33" s="36"/>
-      <c r="U33" s="118"/>
+      <c r="U33" s="109"/>
     </row>
     <row r="34" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="127"/>
+      <c r="A34" s="112"/>
       <c r="B34" s="26">
         <v>7</v>
       </c>
@@ -2674,10 +2674,10 @@
       <c r="R34" s="40"/>
       <c r="S34" s="41"/>
       <c r="T34" s="36"/>
-      <c r="U34" s="118"/>
+      <c r="U34" s="109"/>
     </row>
     <row r="35" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="127"/>
+      <c r="A35" s="112"/>
       <c r="B35" s="26">
         <v>8</v>
       </c>
@@ -2699,7 +2699,7 @@
       <c r="R35" s="40"/>
       <c r="S35" s="41"/>
       <c r="T35" s="36"/>
-      <c r="U35" s="118"/>
+      <c r="U35" s="109"/>
     </row>
     <row r="36" spans="1:25" s="45" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="81"/>
@@ -2722,12 +2722,12 @@
       <c r="R36" s="42"/>
       <c r="S36" s="43"/>
       <c r="T36" s="44"/>
-      <c r="U36" s="119"/>
+      <c r="U36" s="110"/>
       <c r="X36"/>
       <c r="Y36"/>
     </row>
     <row r="37" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="126" t="s">
+      <c r="A37" s="111" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="46">
@@ -2756,12 +2756,12 @@
         <v/>
       </c>
       <c r="T37" s="32"/>
-      <c r="U37" s="114" t="s">
+      <c r="U37" s="125" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="126"/>
+      <c r="A38" s="111"/>
       <c r="B38" s="46">
         <v>2</v>
       </c>
@@ -2788,10 +2788,10 @@
         <v/>
       </c>
       <c r="T38" s="36"/>
-      <c r="U38" s="115"/>
+      <c r="U38" s="126"/>
     </row>
     <row r="39" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="126"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="46">
         <v>3</v>
       </c>
@@ -2823,7 +2823,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="126"/>
+      <c r="A40" s="111"/>
       <c r="B40" s="46">
         <v>4</v>
       </c>
@@ -2850,13 +2850,13 @@
         <v/>
       </c>
       <c r="T40" s="36"/>
-      <c r="U40" s="118">
+      <c r="U40" s="109">
         <f>SUM(S37:S43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="126"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="83"/>
       <c r="C41" s="83"/>
       <c r="D41" s="83"/>
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="T41" s="36"/>
-      <c r="U41" s="118"/>
+      <c r="U41" s="109"/>
     </row>
     <row r="42" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="126"/>
+      <c r="A42" s="111"/>
       <c r="B42" s="46">
         <v>5</v>
       </c>
@@ -2911,10 +2911,10 @@
         <v/>
       </c>
       <c r="T42" s="36"/>
-      <c r="U42" s="118"/>
+      <c r="U42" s="109"/>
     </row>
     <row r="43" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="126"/>
+      <c r="A43" s="111"/>
       <c r="B43" s="46">
         <v>6</v>
       </c>
@@ -2937,14 +2937,14 @@
         <v>35</v>
       </c>
       <c r="S43" s="35" t="str">
-        <f>IF(COUNTIF(L7:N65,"KH*")=0,"",COUNTIF(L7:N65,"KH*"))</f>
+        <f>IF(COUNTIF(L7:N65,"12*")=0,"",COUNTIF(L7:N65,"12*"))</f>
         <v/>
       </c>
       <c r="T43" s="36"/>
-      <c r="U43" s="118"/>
+      <c r="U43" s="109"/>
     </row>
     <row r="44" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="126"/>
+      <c r="A44" s="111"/>
       <c r="B44" s="46">
         <v>7</v>
       </c>
@@ -2966,10 +2966,10 @@
       <c r="R44" s="40"/>
       <c r="S44" s="41"/>
       <c r="T44" s="36"/>
-      <c r="U44" s="118"/>
+      <c r="U44" s="109"/>
     </row>
     <row r="45" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="126"/>
+      <c r="A45" s="111"/>
       <c r="B45" s="46">
         <v>8</v>
       </c>
@@ -2991,7 +2991,7 @@
       <c r="R45" s="40"/>
       <c r="S45" s="41"/>
       <c r="T45" s="36"/>
-      <c r="U45" s="118"/>
+      <c r="U45" s="109"/>
     </row>
     <row r="46" spans="1:25" s="45" customFormat="1" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="81"/>
@@ -3014,12 +3014,12 @@
       <c r="R46" s="42"/>
       <c r="S46" s="43"/>
       <c r="T46" s="44"/>
-      <c r="U46" s="119"/>
+      <c r="U46" s="110"/>
       <c r="X46"/>
       <c r="Y46"/>
     </row>
     <row r="47" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="111" t="s">
+      <c r="A47" s="122" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="26">
@@ -3048,12 +3048,12 @@
         <v/>
       </c>
       <c r="T47" s="32"/>
-      <c r="U47" s="114" t="s">
+      <c r="U47" s="125" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="112"/>
+      <c r="A48" s="123"/>
       <c r="B48" s="26">
         <v>2</v>
       </c>
@@ -3080,10 +3080,10 @@
         <v/>
       </c>
       <c r="T48" s="36"/>
-      <c r="U48" s="115"/>
+      <c r="U48" s="126"/>
     </row>
     <row r="49" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="112"/>
+      <c r="A49" s="123"/>
       <c r="B49" s="26">
         <v>3</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
     </row>
     <row r="50" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="112"/>
+      <c r="A50" s="123"/>
       <c r="B50" s="26">
         <v>4</v>
       </c>
@@ -3142,13 +3142,13 @@
         <v/>
       </c>
       <c r="T50" s="36"/>
-      <c r="U50" s="118">
+      <c r="U50" s="109">
         <f>SUM(S47:S53)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="112"/>
+      <c r="A51" s="123"/>
       <c r="B51" s="83"/>
       <c r="C51" s="83"/>
       <c r="D51" s="83"/>
@@ -3173,10 +3173,10 @@
         <v/>
       </c>
       <c r="T51" s="36"/>
-      <c r="U51" s="118"/>
+      <c r="U51" s="109"/>
     </row>
     <row r="52" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="112"/>
+      <c r="A52" s="123"/>
       <c r="B52" s="26">
         <v>5</v>
       </c>
@@ -3203,10 +3203,10 @@
         <v/>
       </c>
       <c r="T52" s="36"/>
-      <c r="U52" s="118"/>
+      <c r="U52" s="109"/>
     </row>
     <row r="53" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="112"/>
+      <c r="A53" s="123"/>
       <c r="B53" s="26">
         <v>6</v>
       </c>
@@ -3229,14 +3229,14 @@
         <v>35</v>
       </c>
       <c r="S53" s="35" t="str">
-        <f>IF(COUNTIF($O$7:$Q$64,"KH*")=0,"",COUNTIF($O$7:$Q$64,"KH*"))</f>
+        <f>IF(COUNTIF($O$7:$Q$64,"12*")=0,"",COUNTIF($O$7:$Q$64,"12*"))</f>
         <v/>
       </c>
       <c r="T53" s="36"/>
-      <c r="U53" s="118"/>
+      <c r="U53" s="109"/>
     </row>
     <row r="54" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="112"/>
+      <c r="A54" s="123"/>
       <c r="B54" s="26">
         <v>7</v>
       </c>
@@ -3258,10 +3258,10 @@
       <c r="R54" s="40"/>
       <c r="S54" s="41"/>
       <c r="T54" s="36"/>
-      <c r="U54" s="118"/>
+      <c r="U54" s="109"/>
     </row>
     <row r="55" spans="1:25" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="113"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="26">
         <v>8</v>
       </c>
@@ -3283,7 +3283,7 @@
       <c r="R55" s="40"/>
       <c r="S55" s="41"/>
       <c r="T55" s="36"/>
-      <c r="U55" s="119"/>
+      <c r="U55" s="110"/>
     </row>
     <row r="56" spans="1:25" s="45" customFormat="1" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="81"/>
@@ -3303,17 +3303,17 @@
       <c r="O56" s="90"/>
       <c r="P56" s="91"/>
       <c r="Q56" s="91"/>
-      <c r="R56" s="120" t="s">
+      <c r="R56" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="S56" s="121"/>
-      <c r="T56" s="121"/>
-      <c r="U56" s="122"/>
+      <c r="S56" s="130"/>
+      <c r="T56" s="130"/>
+      <c r="U56" s="131"/>
       <c r="X56"/>
       <c r="Y56"/>
     </row>
     <row r="57" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="104" t="s">
+      <c r="A57" s="115" t="s">
         <v>5</v>
       </c>
       <c r="B57" s="46">
@@ -3334,13 +3334,13 @@
       <c r="O57" s="85"/>
       <c r="P57" s="86"/>
       <c r="Q57" s="86"/>
-      <c r="R57" s="123"/>
-      <c r="S57" s="124"/>
-      <c r="T57" s="124"/>
-      <c r="U57" s="125"/>
+      <c r="R57" s="132"/>
+      <c r="S57" s="133"/>
+      <c r="T57" s="133"/>
+      <c r="U57" s="134"/>
     </row>
     <row r="58" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="105"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="46">
         <v>2</v>
       </c>
@@ -3362,13 +3362,13 @@
       <c r="R58" s="40"/>
       <c r="S58" s="41"/>
       <c r="T58" s="36"/>
-      <c r="U58" s="116">
+      <c r="U58" s="127">
         <f>SUM(U10+U20+U30+U40+U50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="105"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="46">
         <v>3</v>
       </c>
@@ -3390,10 +3390,10 @@
       <c r="R59" s="40"/>
       <c r="S59" s="41"/>
       <c r="T59" s="36"/>
-      <c r="U59" s="116"/>
+      <c r="U59" s="127"/>
     </row>
     <row r="60" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="105"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="46">
         <v>4</v>
       </c>
@@ -3415,10 +3415,10 @@
       <c r="R60" s="40"/>
       <c r="S60" s="41"/>
       <c r="T60" s="36"/>
-      <c r="U60" s="116"/>
+      <c r="U60" s="127"/>
     </row>
     <row r="61" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="105"/>
+      <c r="A61" s="116"/>
       <c r="B61" s="83"/>
       <c r="C61" s="83"/>
       <c r="D61" s="83"/>
@@ -3438,10 +3438,10 @@
       <c r="R61" s="40"/>
       <c r="S61" s="41"/>
       <c r="T61" s="36"/>
-      <c r="U61" s="116"/>
+      <c r="U61" s="127"/>
     </row>
     <row r="62" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="105"/>
+      <c r="A62" s="116"/>
       <c r="B62" s="46">
         <v>5</v>
       </c>
@@ -3463,10 +3463,10 @@
       <c r="R62" s="40"/>
       <c r="S62" s="41"/>
       <c r="T62" s="36"/>
-      <c r="U62" s="116"/>
+      <c r="U62" s="127"/>
     </row>
     <row r="63" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="105"/>
+      <c r="A63" s="116"/>
       <c r="B63" s="46">
         <v>6</v>
       </c>
@@ -3488,10 +3488,10 @@
       <c r="R63" s="40"/>
       <c r="S63" s="41"/>
       <c r="T63" s="36"/>
-      <c r="U63" s="116"/>
+      <c r="U63" s="127"/>
     </row>
     <row r="64" spans="1:25" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="105"/>
+      <c r="A64" s="116"/>
       <c r="B64" s="46">
         <v>7</v>
       </c>
@@ -3513,10 +3513,10 @@
       <c r="R64" s="40"/>
       <c r="S64" s="41"/>
       <c r="T64" s="36"/>
-      <c r="U64" s="116"/>
+      <c r="U64" s="127"/>
     </row>
     <row r="65" spans="1:21" ht="10.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="106"/>
+      <c r="A65" s="117"/>
       <c r="B65" s="46">
         <v>8</v>
       </c>
@@ -3538,7 +3538,7 @@
       <c r="R65" s="48"/>
       <c r="S65" s="43"/>
       <c r="T65" s="49"/>
-      <c r="U65" s="117"/>
+      <c r="U65" s="128"/>
     </row>
     <row r="66" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="50"/>
@@ -3559,24 +3559,24 @@
       <c r="H66" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="I66" s="130" t="s">
+      <c r="I66" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="J66" s="131"/>
-      <c r="K66" s="132"/>
-      <c r="L66" s="133" t="s">
+      <c r="J66" s="96"/>
+      <c r="K66" s="97"/>
+      <c r="L66" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="M66" s="134"/>
-      <c r="N66" s="135"/>
+      <c r="M66" s="99"/>
+      <c r="N66" s="100"/>
       <c r="O66" s="58"/>
       <c r="P66" s="58"/>
       <c r="Q66" s="59"/>
-      <c r="R66" s="136" t="s">
+      <c r="R66" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="S66" s="137"/>
-      <c r="T66" s="138"/>
+      <c r="S66" s="102"/>
+      <c r="T66" s="103"/>
       <c r="U66" s="60"/>
     </row>
     <row r="67" spans="1:21" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3603,57 +3603,57 @@
         <f>COUNTIF(C7:T65,"8*")</f>
         <v>0</v>
       </c>
-      <c r="I67" s="139">
+      <c r="I67" s="104">
         <f>COUNTIF(C7:T65,"9*")</f>
         <v>0</v>
       </c>
-      <c r="J67" s="140"/>
-      <c r="K67" s="141"/>
-      <c r="L67" s="139">
+      <c r="J67" s="105"/>
+      <c r="K67" s="106"/>
+      <c r="L67" s="104">
         <f>COUNTIF(C7:T65,"10*")+COUNTIF(C7:T65,"11*")</f>
         <v>0</v>
       </c>
-      <c r="M67" s="140"/>
-      <c r="N67" s="141"/>
-      <c r="O67" s="139"/>
-      <c r="P67" s="140"/>
-      <c r="Q67" s="141"/>
-      <c r="R67" s="139">
+      <c r="M67" s="105"/>
+      <c r="N67" s="106"/>
+      <c r="O67" s="104"/>
+      <c r="P67" s="105"/>
+      <c r="Q67" s="106"/>
+      <c r="R67" s="104">
         <f>COUNTIF(C7:T65,"12*")</f>
         <v>0</v>
       </c>
-      <c r="S67" s="140"/>
-      <c r="T67" s="141"/>
+      <c r="S67" s="105"/>
+      <c r="T67" s="106"/>
       <c r="U67" s="60"/>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="107" t="s">
+      <c r="A68" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="B68" s="108"/>
-      <c r="C68" s="108"/>
-      <c r="D68" s="108"/>
-      <c r="E68" s="108"/>
-      <c r="F68" s="108"/>
-      <c r="G68" s="108" t="s">
+      <c r="B68" s="119"/>
+      <c r="C68" s="119"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="119"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="H68" s="108"/>
-      <c r="I68" s="108"/>
-      <c r="J68" s="108"/>
-      <c r="K68" s="108"/>
-      <c r="L68" s="109" t="s">
+      <c r="H68" s="119"/>
+      <c r="I68" s="119"/>
+      <c r="J68" s="119"/>
+      <c r="K68" s="119"/>
+      <c r="L68" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="M68" s="109"/>
-      <c r="N68" s="109"/>
-      <c r="O68" s="109"/>
-      <c r="P68" s="109"/>
-      <c r="Q68" s="109"/>
-      <c r="R68" s="109"/>
-      <c r="S68" s="109"/>
-      <c r="T68" s="109"/>
-      <c r="U68" s="110"/>
+      <c r="M68" s="120"/>
+      <c r="N68" s="120"/>
+      <c r="O68" s="120"/>
+      <c r="P68" s="120"/>
+      <c r="Q68" s="120"/>
+      <c r="R68" s="120"/>
+      <c r="S68" s="120"/>
+      <c r="T68" s="120"/>
+      <c r="U68" s="121"/>
     </row>
     <row r="69" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="65"/>
@@ -3683,31 +3683,31 @@
       <c r="D71" s="72"/>
       <c r="E71" s="72"/>
       <c r="F71" s="72"/>
-      <c r="G71" s="142" t="s">
+      <c r="G71" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="H71" s="142"/>
-      <c r="I71" s="142"/>
-      <c r="J71" s="142"/>
-      <c r="K71" s="142"/>
-      <c r="L71" s="142"/>
-      <c r="M71" s="142"/>
-      <c r="N71" s="142"/>
-      <c r="O71" s="142"/>
-      <c r="P71" s="142"/>
-      <c r="Q71" s="142"/>
-      <c r="R71" s="142"/>
-      <c r="S71" s="142"/>
-      <c r="T71" s="142"/>
-      <c r="U71" s="143"/>
+      <c r="H71" s="107"/>
+      <c r="I71" s="107"/>
+      <c r="J71" s="107"/>
+      <c r="K71" s="107"/>
+      <c r="L71" s="107"/>
+      <c r="M71" s="107"/>
+      <c r="N71" s="107"/>
+      <c r="O71" s="107"/>
+      <c r="P71" s="107"/>
+      <c r="Q71" s="107"/>
+      <c r="R71" s="107"/>
+      <c r="S71" s="107"/>
+      <c r="T71" s="107"/>
+      <c r="U71" s="108"/>
     </row>
     <row r="72" spans="1:21" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="128"/>
-      <c r="B72" s="129"/>
-      <c r="C72" s="129"/>
-      <c r="D72" s="129"/>
-      <c r="E72" s="129"/>
-      <c r="F72" s="129"/>
+      <c r="A72" s="93"/>
+      <c r="B72" s="94"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="94"/>
+      <c r="E72" s="94"/>
+      <c r="F72" s="94"/>
       <c r="G72" s="73"/>
       <c r="H72" s="74"/>
       <c r="I72" s="74"/>
@@ -3727,21 +3727,14 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="39">
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:N66"/>
-    <mergeCell ref="R66:T66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="L67:N67"/>
-    <mergeCell ref="O67:Q67"/>
-    <mergeCell ref="R67:T67"/>
-    <mergeCell ref="L71:U71"/>
-    <mergeCell ref="G71:K71"/>
-    <mergeCell ref="U20:U26"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="U30:U36"/>
-    <mergeCell ref="A7:A15"/>
-    <mergeCell ref="U40:U46"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:U5"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A57:A65"/>
     <mergeCell ref="A68:F68"/>
@@ -3758,14 +3751,21 @@
     <mergeCell ref="U37:U38"/>
     <mergeCell ref="A37:A45"/>
     <mergeCell ref="A27:A35"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:U5"/>
+    <mergeCell ref="U20:U26"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="U30:U36"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="U40:U46"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="R66:T66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="O67:Q67"/>
+    <mergeCell ref="R67:T67"/>
+    <mergeCell ref="L71:U71"/>
+    <mergeCell ref="G71:K71"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 N2:S2" xr:uid="{00DA29C0-4EEF-4ADD-985B-DBFA474DE47C}">
